--- a/2022/Mount3/Mount3_Members_final.xlsx
+++ b/2022/Mount3/Mount3_Members_final.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مواطنون ومواطنات في دولة</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
